--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488095_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488095_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2204</v>
+        <v>3.9291</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1605</v>
+        <v>3.2624</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0599</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.5039</v>
@@ -688,13 +688,13 @@
         <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>1.331</v>
+        <v>1.0397</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2975</v>
+        <v>0.3994</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0335</v>
+        <v>0.6403</v>
       </c>
       <c r="V3" t="n">
         <v>0.1962</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0007</v>
+        <v>3.7688</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5266</v>
+        <v>4.3228</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5259</v>
+        <v>-0.554</v>
       </c>
       <c r="G4" t="n">
         <v>0.603</v>
@@ -766,13 +766,13 @@
         <v>0.3964</v>
       </c>
       <c r="S4" t="n">
-        <v>0.587</v>
+        <v>0.3552</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2534</v>
+        <v>0.0496</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3336</v>
+        <v>0.3055</v>
       </c>
       <c r="V4" t="n">
         <v>2.4142</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2922</v>
+        <v>3.4783</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0283</v>
+        <v>2.1302</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2638</v>
+        <v>1.3481</v>
       </c>
       <c r="G5" t="n">
         <v>3.8285</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0672</v>
+        <v>0.2533</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3706</v>
+        <v>-0.2687</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4378</v>
+        <v>0.522</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6036</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7292</v>
+        <v>0.8343</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4683</v>
+        <v>1.2645</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7391</v>
+        <v>-0.4302</v>
       </c>
       <c r="G6" t="n">
         <v>2.4821</v>
@@ -922,13 +922,13 @@
         <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.407</v>
+        <v>-0.3019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.132</v>
+        <v>-0.3358</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.275</v>
+        <v>0.0339</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5441</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3093</v>
+        <v>0.355</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6397</v>
+        <v>0.7416</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3304</v>
+        <v>-0.3866</v>
       </c>
       <c r="G7" t="n">
         <v>1.2865</v>
@@ -1000,13 +1000,13 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1843</v>
+        <v>-0.1386</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2496</v>
+        <v>-0.1477</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0653</v>
+        <v>0.0091</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1784</v>
+        <v>-0.1948</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4533</v>
+        <v>-0.7984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6317</v>
+        <v>0.6037</v>
       </c>
       <c r="G8" t="n">
         <v>-2.8181</v>
@@ -1078,13 +1078,13 @@
         <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.598</v>
+        <v>0.2249</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1213</v>
+        <v>-0.2237</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4767</v>
+        <v>0.4486</v>
       </c>
       <c r="V8" t="n">
         <v>1.0109</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9546</v>
+        <v>-0.8079</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1883</v>
+        <v>-0.1259</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7663</v>
+        <v>-0.6821</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0884</v>
@@ -1156,13 +1156,13 @@
         <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5371</v>
+        <v>0.6837</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2423</v>
+        <v>0.3047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2947</v>
+        <v>0.379</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7997</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3264</v>
+        <v>-1.661</v>
       </c>
       <c r="E10" t="n">
-        <v>1.889</v>
+        <v>1.442</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2154</v>
+        <v>-3.1031</v>
       </c>
       <c r="G10" t="n">
         <v>0.5079</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7871</v>
+        <v>0.4525</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0589</v>
+        <v>-0.388</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7282</v>
+        <v>0.8405</v>
       </c>
       <c r="V10" t="n">
         <v>-3.0178</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7208</v>
+        <v>-2.2894</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4</v>
+        <v>-0.8283</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3208</v>
+        <v>-1.4612</v>
       </c>
       <c r="G11" t="n">
         <v>-0.26</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2625</v>
+        <v>0.1688</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8736</v>
+        <v>-0.3018</v>
       </c>
       <c r="U11" t="n">
-        <v>0.611</v>
+        <v>0.4707</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2071</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.4574</v>
+        <v>-7.8295</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7935</v>
+        <v>-9.2218</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3362</v>
+        <v>1.3923</v>
       </c>
       <c r="G12" t="n">
         <v>-4.904</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.025</v>
+        <v>0.6029</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8698</v>
+        <v>-0.298</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8448</v>
+        <v>0.901</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3479</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.494999999999999</v>
+        <v>3.8069</v>
       </c>
       <c r="E13" t="n">
-        <v>6.101299999999998</v>
+        <v>6.413099999999996</v>
       </c>
       <c r="F13" t="n">
         <v>-2.6063</v>
@@ -1468,10 +1468,10 @@
         <v>9.911000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>3.0286</v>
+        <v>3.3405</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5222</v>
+        <v>-1.21</v>
       </c>
       <c r="U13" t="n">
         <v>4.5506</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.458</v>
+        <v>3.5517</v>
       </c>
       <c r="E14" t="n">
-        <v>2.741</v>
+        <v>4.3973</v>
       </c>
       <c r="F14" t="n">
-        <v>0.717</v>
+        <v>-0.8457</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1794</v>
+        <v>0.6414</v>
       </c>
       <c r="H14" t="n">
-        <v>0.499</v>
+        <v>1.1772</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3196</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1498</v>
+        <v>1.8835</v>
       </c>
       <c r="K14" t="n">
-        <v>1.628</v>
+        <v>2.4421</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4782</v>
+        <v>-0.5586</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9704</v>
+        <v>-1.242</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.129</v>
+        <v>-1.2648</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1586</v>
+        <v>0.0228</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3876</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4082</v>
+        <v>-0.5901</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9877</v>
+        <v>-0.5285</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4205</v>
+        <v>-0.0616</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4828</v>
+        <v>4.4914</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6036</v>
+        <v>5.0246</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1207</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6995</v>
+        <v>2.3609</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9899</v>
+        <v>1.6205</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2904</v>
+        <v>0.7405</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6414</v>
+        <v>0.1794</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1772</v>
+        <v>0.499</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.3196</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8835</v>
+        <v>1.1498</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4421</v>
+        <v>1.628</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5586</v>
+        <v>-0.4782</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.242</v>
+        <v>-0.9704</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2648</v>
+        <v>-1.129</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0228</v>
+        <v>0.1586</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4423</v>
+        <v>0.3111</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.1329</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5063</v>
+        <v>0.444</v>
       </c>
       <c r="V15" t="n">
-        <v>4.4914</v>
+        <v>0.4828</v>
       </c>
       <c r="W15" t="n">
-        <v>5.0246</v>
+        <v>0.6036</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5331</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5603</v>
+        <v>1.5499</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8105</v>
+        <v>0.9124</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7498</v>
+        <v>0.6375</v>
       </c>
       <c r="G16" t="n">
         <v>0.791</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1747</v>
+        <v>0.1643</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2386</v>
+        <v>-0.1367</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4133</v>
+        <v>0.301</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FIDALGO PEDUZZI</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0894</v>
+        <v>0.9633</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7889</v>
+        <v>1.6928</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3005</v>
+        <v>-0.7295</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2191</v>
+        <v>-0.1065</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8637</v>
+        <v>1.0128</v>
       </c>
       <c r="I17" t="n">
-        <v>4.0828</v>
+        <v>-1.1193</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9367</v>
+        <v>1.3452</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0674</v>
+        <v>1.944</v>
       </c>
       <c r="L17" t="n">
-        <v>4.8693</v>
+        <v>-0.5988</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7176</v>
+        <v>-1.4517</v>
       </c>
       <c r="N17" t="n">
         <v>-0.9312</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7864</v>
+        <v>-0.5205</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9733</v>
+        <v>0.7929</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6273</v>
+        <v>-0.3267</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1834</v>
+        <v>-0.256</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8107</v>
+        <v>-0.0708</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2163</v>
+        <v>0.6036</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>A. FIDALGO PEDUZZI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5173</v>
+        <v>0.5767</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3872</v>
+        <v>0.5851</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8699</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1065</v>
+        <v>3.2191</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0128</v>
+        <v>-0.8637</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1193</v>
+        <v>4.0828</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3452</v>
+        <v>4.9367</v>
       </c>
       <c r="K20" t="n">
-        <v>1.944</v>
+        <v>0.0674</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5988</v>
+        <v>4.8693</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4517</v>
+        <v>-1.7176</v>
       </c>
       <c r="N20" t="n">
         <v>-0.9312</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5205</v>
+        <v>-0.7864</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7929</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1147</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5616</v>
+        <v>-0.3871</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2112</v>
+        <v>0.5019</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6036</v>
+        <v>0.2163</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2163</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0331</v>
+        <v>0.1956</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6368</v>
+        <v>0.0139</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6038</v>
+        <v>0.1817</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4296</v>
+        <v>-0.2501</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2165</v>
+        <v>-0.5448</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2131</v>
+        <v>0.2947</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2145</v>
+        <v>0.8544</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0265</v>
+        <v>0.3165</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2411</v>
+        <v>0.5379</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6442</v>
+        <v>-1.1044</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.19</v>
+        <v>-0.8613</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4542</v>
+        <v>-0.2431</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1346</v>
+        <v>-0.5635</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4223</v>
+        <v>-0.8405</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7123</v>
+        <v>0.277</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2666</v>
+        <v>0.2163</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2666</v>
+        <v>0.2163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.8308</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3936</v>
+        <v>0.0256</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2349</v>
+        <v>-0.8565</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2501</v>
+        <v>-1.4296</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5448</v>
+        <v>-0.2165</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2947</v>
+        <v>-1.2131</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8544</v>
+        <v>0.2145</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3165</v>
+        <v>-0.0265</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5379</v>
+        <v>0.2411</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1044</v>
+        <v>-1.6442</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8613</v>
+        <v>-0.19</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2431</v>
+        <v>-1.4542</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3876</v>
+        <v>0.2707</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2479</v>
+        <v>-0.1889</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1396</v>
+        <v>0.4596</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2163</v>
+        <v>-0.2666</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2163</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8851</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1872</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6137</v>
+        <v>-0.6979</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8695000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.0156</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4492</v>
+        <v>-2.947</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7418</v>
+        <v>-0.4362</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7074</v>
+        <v>-2.5109</v>
       </c>
       <c r="G24" t="n">
         <v>0.3929</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4548</v>
+        <v>-0.9526</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8736</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5812</v>
+        <v>-0.3846</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5944</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4587</v>
+        <v>-4.379</v>
       </c>
       <c r="E25" t="n">
         <v>-4.2551</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2036</v>
+        <v>-0.124</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6886</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3825</v>
+        <v>-0.3029</v>
       </c>
       <c r="T25" t="n">
         <v>-0.433</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0505</v>
+        <v>0.1301</v>
       </c>
       <c r="V25" t="n">
         <v>1.2071</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.0232</v>
+        <v>-4.4799</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6784</v>
+        <v>-3.2709</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3448</v>
+        <v>-1.209</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7527</v>
@@ -2482,13 +2482,13 @@
         <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0021</v>
+        <v>-0.4588</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2993</v>
+        <v>-0.8918</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2972</v>
+        <v>0.433</v>
       </c>
       <c r="V26" t="n">
         <v>-0.4577</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.4949</v>
+        <v>-2.8157</v>
       </c>
       <c r="E27" t="n">
-        <v>2.606200000000002</v>
+        <v>2.606200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.1012</v>
+        <v>-5.4222</v>
       </c>
       <c r="G27" t="n">
         <v>-5.3652</v>
@@ -2557,19 +2557,19 @@
         <v>-9.911099999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>9.911200000000001</v>
+        <v>9.911199999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.0286</v>
+        <v>-2.3494</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.5506</v>
+        <v>-4.550599999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>1.522</v>
+        <v>2.2012</v>
       </c>
       <c r="V27" t="n">
-        <v>4.8988</v>
+        <v>4.898799999999999</v>
       </c>
       <c r="W27" t="n">
         <v>7.6351</v>
